--- a/python/release_02_1/input/关键字-CAPL函数映射表0125.xlsx
+++ b/python/release_02_1/input/关键字-CAPL函数映射表0125.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="HIL用例关键字说明" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="513">
   <si>
     <t>编号</t>
   </si>
@@ -290,6 +290,18 @@
   </si>
   <si>
     <t>g_HIL_Bus_Swc_Condition_ReadConfig</t>
+  </si>
+  <si>
+    <t>Enable_XCP</t>
+  </si>
+  <si>
+    <t>g_HIL_XCP_Swc_Enable_XCP</t>
+  </si>
+  <si>
+    <t>Disable_XCP</t>
+  </si>
+  <si>
+    <t>g_HIL_XCP_Swc_Disable_XCP</t>
   </si>
   <si>
     <t>TC_CANTest</t>
@@ -2048,7 +2060,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2188,6 +2200,17 @@
     </border>
     <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -2308,7 +2331,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2320,34 +2343,34 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2432,7 +2455,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2592,11 +2615,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2662,7 +2700,7 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="0">
-    <open main="169" threadCnt="1"/>
+    <open main="155" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="0" sheetStid="2">
         <open main="1" threadCnt="1"/>
@@ -2954,7 +2992,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3468,30 +3506,56 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="51">
+      <c r="A39" s="53">
         <v>38</v>
       </c>
-      <c r="B39" s="52" t="s">
+      <c r="B39" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46" t="s">
+      <c r="C39" s="55"/>
+      <c r="D39" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="E39" s="46"/>
+      <c r="E39" s="55"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40">
+      <c r="A40" s="56">
         <v>39</v>
       </c>
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="57" t="s">
         <v>83</v>
       </c>
       <c r="C40" s="46"/>
-      <c r="D40" s="54" t="s">
+      <c r="D40" s="58" t="s">
         <v>84</v>
       </c>
       <c r="E40" s="46"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="56">
+        <v>40</v>
+      </c>
+      <c r="B41" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="56"/>
+      <c r="D41" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="56"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="56">
+        <v>41</v>
+      </c>
+      <c r="B42" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="56"/>
+      <c r="D42" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="56"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -3538,13 +3602,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:4">
@@ -3552,13 +3616,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:4">
@@ -3566,13 +3630,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="13.5" spans="1:4">
@@ -3580,13 +3644,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="1:4">
@@ -3594,13 +3658,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" ht="13.5" spans="1:4">
@@ -3608,13 +3672,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" ht="13.5" spans="1:4">
@@ -3622,13 +3686,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" ht="13.5" spans="1:4">
@@ -3636,13 +3700,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" ht="13.5" spans="1:4">
@@ -3650,13 +3714,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" ht="13.5" spans="1:4">
@@ -3664,13 +3728,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="13.5" spans="1:4">
@@ -3678,13 +3742,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" ht="13.5" spans="1:4">
@@ -3692,13 +3756,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:4">
@@ -3706,13 +3770,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" ht="13.5" spans="1:4">
@@ -3720,13 +3784,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" ht="13.5" spans="1:4">
@@ -3734,13 +3798,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" ht="13.5" spans="1:5">
@@ -3748,13 +3812,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E17" s="29"/>
     </row>
@@ -3763,13 +3827,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" ht="13.5" spans="1:5">
@@ -3777,13 +3841,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E19" s="29"/>
     </row>
@@ -3792,13 +3856,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E20" s="29"/>
     </row>
@@ -3807,13 +3871,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E21" s="29"/>
     </row>
@@ -3822,13 +3886,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" ht="13.5" spans="1:4">
@@ -3836,13 +3900,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" ht="13.5" spans="1:4">
@@ -3850,13 +3914,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" ht="13.5" spans="1:4">
@@ -3864,13 +3928,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" ht="13.5" spans="1:4">
@@ -3878,13 +3942,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" ht="13.5" spans="1:4">
@@ -3892,13 +3956,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" ht="13.5" spans="1:4">
@@ -3906,13 +3970,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" ht="13.5" spans="1:4">
@@ -3920,13 +3984,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" ht="13.5" spans="1:4">
@@ -3934,13 +3998,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" ht="13.5" spans="1:4">
@@ -3948,1546 +4012,1546 @@
         <v>30</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" ht="13.5" spans="1:4">
       <c r="A32" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" ht="13.5" spans="1:4">
       <c r="A33" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" ht="13.5" spans="1:4">
       <c r="A34" s="6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" ht="13.5" spans="1:4">
       <c r="A35" s="6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" ht="13.5" spans="1:4">
       <c r="A36" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" ht="13.5" spans="1:4">
       <c r="A37" s="6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" ht="13.5" spans="1:4">
       <c r="A38" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" ht="13.5" spans="1:4">
       <c r="A39" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" ht="13.5" spans="1:4">
       <c r="A40" s="6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" ht="13.5" spans="1:4">
       <c r="A41" s="6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" ht="13.5" spans="1:4">
       <c r="A42" s="6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" ht="13.5" spans="1:4">
       <c r="A43" s="6">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" ht="13.5" spans="1:4">
       <c r="A44" s="6">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" ht="13.5" spans="1:4">
       <c r="A45" s="6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" ht="13.5" spans="1:4">
       <c r="A46" s="6">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" ht="13.5" spans="1:4">
       <c r="A47" s="6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" ht="13.5" spans="1:4">
       <c r="A48" s="6">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" ht="13.5" spans="1:5">
       <c r="A49" s="6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E49" s="25"/>
     </row>
     <row r="50" ht="13.5" spans="1:4">
       <c r="A50" s="6">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" ht="13.5" spans="1:4">
       <c r="A51" s="6">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" ht="13.5" spans="1:4">
       <c r="A52" s="6">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" ht="13.5" spans="1:4">
       <c r="A53" s="6">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" ht="13.5" spans="1:4">
       <c r="A54" s="6">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C54" s="31" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" ht="13.5" spans="1:4">
       <c r="A55" s="6">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C55" s="31" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" ht="13.5" spans="1:4">
       <c r="A56" s="6">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C56" s="31" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" ht="13.5" spans="1:4">
       <c r="A57" s="6">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C57" s="31" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" ht="13.5" spans="1:4">
       <c r="A58" s="6">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C58" s="31" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" ht="13.5" spans="1:4">
       <c r="A59" s="6">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" ht="13.5" spans="1:4">
       <c r="A60" s="6">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C60" s="32" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" ht="13.5" spans="1:4">
       <c r="A61" s="6">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C61" s="31" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" ht="13.5" spans="1:4">
       <c r="A62" s="6">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" ht="13.5" spans="1:4">
       <c r="A63" s="6">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" ht="13.5" spans="1:4">
       <c r="A64" s="6">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" ht="13.5" spans="1:4">
       <c r="A65" s="6">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" ht="13.5" spans="1:4">
       <c r="A66" s="6">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" ht="13.5" spans="1:4">
       <c r="A67" s="6">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" ht="13.5" spans="1:4">
       <c r="A68" s="6">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C68" s="27" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" ht="13.5" spans="1:4">
       <c r="A69" s="6">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C69" s="31" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" ht="13.5" spans="1:4">
       <c r="A70" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" ht="27" spans="1:4">
       <c r="A71" s="6">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C71" s="31" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" ht="13.5" spans="1:4">
       <c r="A72" s="6">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" ht="13.5" spans="1:4">
       <c r="A73" s="6">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74" ht="13.5" spans="1:4">
       <c r="A74" s="6">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" ht="13.5" spans="1:4">
       <c r="A75" s="6">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" ht="13.5" spans="1:4">
       <c r="A76" s="6">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" ht="13.5" spans="1:4">
       <c r="A77" s="6">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78" ht="13.5" spans="1:4">
       <c r="A78" s="6">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="79" ht="13.5" spans="1:4">
       <c r="A79" s="6">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C79" s="35" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="80" ht="13.5" spans="1:4">
       <c r="A80" s="6">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" ht="13.5" spans="1:4">
       <c r="A81" s="6">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C81" s="35" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82" ht="13.5" spans="1:4">
       <c r="A82" s="6">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="83" ht="13.5" spans="1:4">
       <c r="A83" s="6">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84" ht="13.5" spans="1:4">
       <c r="A84" s="6">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="85" ht="13.5" spans="1:4">
       <c r="A85" s="6">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" ht="13.5" spans="1:4">
       <c r="A86" s="6">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="87" ht="13.5" spans="1:4">
       <c r="A87" s="6">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88" ht="13.5" spans="1:4">
       <c r="A88" s="6">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C88" s="34" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89" ht="13.5" spans="1:4">
       <c r="A89" s="6">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C89" s="34" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90" ht="13.5" spans="1:4">
       <c r="A90" s="6">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" ht="13.5" spans="1:4">
       <c r="A91" s="6">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="92" ht="13.5" spans="1:4">
       <c r="A92" s="6">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" ht="13.5" spans="1:4">
       <c r="A93" s="6">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" ht="13.5" spans="1:4">
       <c r="A94" s="6">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B94" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="95" ht="13.5" spans="1:4">
       <c r="A95" s="6">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B95" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" ht="13.5" spans="1:4">
       <c r="A96" s="6">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B96" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="97" ht="13.5" spans="1:4">
       <c r="A97" s="6">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C97" s="35" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="98" ht="13.5" spans="1:4">
       <c r="A98" s="6">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B98" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" ht="13.5" spans="1:4">
       <c r="A99" s="6">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C99" s="35" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="100" ht="13.5" spans="1:4">
       <c r="A100" s="6">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B100" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C100" s="35" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="101" ht="13.5" spans="1:4">
       <c r="A101" s="6">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B101" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C101" s="35" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" ht="13.5" spans="1:4">
       <c r="A102" s="6">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B102" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C102" s="35" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="103" ht="13.5" spans="1:4">
       <c r="A103" s="6">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B103" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C103" s="35" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="104" ht="13.5" spans="1:4">
       <c r="A104" s="6">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B104" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C104" s="35" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="105" ht="13.5" spans="1:4">
       <c r="A105" s="6">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B105" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C105" s="35" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="106" ht="13.5" spans="1:4">
       <c r="A106" s="6">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B106" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C106" s="35" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="107" ht="13.5" spans="1:4">
       <c r="A107" s="6">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C107" s="36" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="108" ht="13.5" spans="1:4">
       <c r="A108" s="6">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C108" s="36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="109" ht="13.5" spans="1:4">
       <c r="A109" s="6">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C109" s="36" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="110" ht="13.5" spans="1:4">
       <c r="A110" s="6">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B110" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C110" s="36" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="111" ht="13.5" spans="1:6">
       <c r="A111" s="6">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C111" s="36" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E111" s="38"/>
       <c r="F111" s="39"/>
     </row>
     <row r="112" ht="13.5" spans="1:6">
       <c r="A112" s="6">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C112" s="36" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E112" s="38"/>
       <c r="F112" s="39"/>
     </row>
     <row r="113" ht="13.5" spans="1:6">
       <c r="A113" s="6">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B113" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C113" s="36" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E113" s="38"/>
       <c r="F113" s="39"/>
     </row>
     <row r="114" ht="13.5" spans="1:6">
       <c r="A114" s="6">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B114" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C114" s="36" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E114" s="38"/>
       <c r="F114" s="39"/>
     </row>
     <row r="115" ht="13.5" spans="1:6">
       <c r="A115" s="6">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B115" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C115" s="37" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E115" s="38"/>
       <c r="F115" s="38"/>
     </row>
     <row r="116" ht="13.5" spans="1:6">
       <c r="A116" s="6">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B116" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C116" s="37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E116" s="38"/>
       <c r="F116" s="39"/>
     </row>
     <row r="117" ht="13.5" spans="1:6">
       <c r="A117" s="6">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B117" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C117" s="37" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E117" s="38"/>
       <c r="F117" s="39"/>
     </row>
     <row r="118" ht="13.5" spans="1:6">
       <c r="A118" s="6">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B118" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E118" s="38"/>
       <c r="F118" s="39"/>
     </row>
     <row r="119" ht="13.5" spans="1:6">
       <c r="A119" s="6">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B119" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E119" s="38"/>
       <c r="F119" s="39"/>
     </row>
     <row r="120" ht="13.5" spans="1:6">
       <c r="A120" s="6">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B120" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E120" s="38"/>
       <c r="F120" s="39"/>
     </row>
     <row r="121" ht="13.5" spans="1:6">
       <c r="A121" s="6">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B121" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E121" s="38"/>
       <c r="F121" s="39"/>
     </row>
     <row r="122" ht="13.5" spans="1:6">
       <c r="A122" s="6">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B122" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C122" s="37" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E122" s="38"/>
       <c r="F122" s="39"/>
     </row>
     <row r="123" ht="13.5" spans="1:6">
       <c r="A123" s="6">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B123" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C123" s="36" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E123" s="38"/>
       <c r="F123" s="38"/>
     </row>
     <row r="124" ht="13.5" spans="1:4">
       <c r="A124" s="6">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B124" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C124" s="36" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="125" ht="13.5" spans="1:4">
       <c r="A125" s="6">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B125" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C125" s="36" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="126" ht="13.5" spans="1:4">
       <c r="A126" s="6">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B126" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C126" s="36" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="127" ht="13.5" spans="1:4">
       <c r="A127" s="6">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B127" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C127" s="36" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="128" ht="13.5" spans="1:4">
       <c r="A128" s="6">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B128" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C128" s="37" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="129" ht="13.5" spans="1:4">
       <c r="A129" s="6">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B129" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C129" s="37" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="130" ht="13.5" spans="1:4">
       <c r="A130" s="6">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B130" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C130" s="37" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="131" ht="13.5" spans="1:4">
       <c r="A131" s="6">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B131" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C131" s="37" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="132" ht="13.5" spans="1:4">
       <c r="A132" s="6">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B132" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C132" s="37" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="133" ht="13.5" spans="1:4">
       <c r="A133" s="6">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B133" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C133" s="37" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="134" ht="13.5" spans="1:4">
       <c r="A134" s="6">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B134" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C134" s="37" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="135" ht="13.5" spans="1:4">
       <c r="A135" s="6">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B135" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C135" s="37" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="136" ht="27" spans="1:4">
       <c r="A136" s="6">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C136" s="40" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="137" ht="27" spans="1:4">
       <c r="A137" s="6">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C137" s="17"/>
       <c r="D137" s="9" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="138" ht="27" spans="1:4">
       <c r="A138" s="6">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B138" s="33" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C138" s="17"/>
       <c r="D138" s="9" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="139" ht="40.5" spans="1:4">
       <c r="A139" s="6">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B139" s="41" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C139" s="42"/>
       <c r="D139" s="9" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -5498,7 +5562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D1 A2:A70 A72:A137 A138:B139 F124:Q139 D139 C116:D136 G111:Q123 D115 C6:C46 C55:C57 C47:D54 C68:C70 C59:D67 A71:D71 C72:D96 D97 C98:D105 D106 F1:Q110 C107:D114" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1 B138:B139 F124:Q139 D139 C116:D136 G111:Q123 D115 C6:C46 C55:C57 C47:D54 C68:C70 C59:D67 B71:D71 C72:D96 D97 C98:D105 D106 F1:Q110 C107:D114" numberStoredAsText="1"/>
   </ignoredErrors>
   <picture r:id="rId1"/>
 </worksheet>
@@ -5539,13 +5603,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:4">
@@ -5553,13 +5617,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:5">
@@ -5567,13 +5631,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E4" s="25"/>
     </row>
@@ -5582,13 +5646,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E5" s="25"/>
     </row>
@@ -5597,13 +5661,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E6" s="25"/>
     </row>
@@ -5612,13 +5676,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E7" s="25"/>
     </row>
@@ -5627,13 +5691,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E8" s="25"/>
     </row>
@@ -5642,13 +5706,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E9" s="25"/>
     </row>
@@ -5657,13 +5721,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E10" s="25"/>
     </row>
@@ -5672,13 +5736,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E11" s="25"/>
     </row>
@@ -5687,13 +5751,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E12" s="25"/>
     </row>
@@ -5702,13 +5766,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E13" s="25"/>
     </row>
@@ -5717,13 +5781,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E14" s="25"/>
     </row>
@@ -5732,13 +5796,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E15" s="25"/>
     </row>
@@ -5747,13 +5811,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E16" s="25"/>
     </row>
@@ -5762,13 +5826,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E17" s="25"/>
     </row>
@@ -5777,13 +5841,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E18" s="25"/>
     </row>
@@ -5792,13 +5856,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E19" s="25"/>
     </row>
@@ -5807,13 +5871,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E20" s="25"/>
     </row>
@@ -5822,13 +5886,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E21" s="25"/>
     </row>
@@ -5837,13 +5901,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E22" s="25"/>
     </row>
@@ -5852,13 +5916,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E23" s="25"/>
     </row>
@@ -5867,13 +5931,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E24" s="25"/>
     </row>
@@ -5882,13 +5946,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E25" s="25"/>
     </row>
@@ -5897,13 +5961,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E26" s="25"/>
     </row>
@@ -5912,13 +5976,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E27" s="25"/>
     </row>
@@ -5927,13 +5991,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E28" s="25"/>
     </row>
@@ -5982,13 +6046,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:4">
@@ -5996,13 +6060,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:4">
@@ -6010,13 +6074,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" ht="13.5" spans="1:4">
@@ -6024,13 +6088,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="1:4">
@@ -6038,13 +6102,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" ht="13.5" spans="1:4">
@@ -6052,13 +6116,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" ht="13.5" spans="1:4">
@@ -6066,13 +6130,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" ht="13.5" spans="1:4">
@@ -6080,13 +6144,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" ht="13.5" spans="1:4">
@@ -6094,13 +6158,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" ht="13.5" spans="1:4">
@@ -6108,277 +6172,277 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" ht="13.5" spans="1:4">
       <c r="A12" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" ht="13.5" spans="1:4">
       <c r="A13" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:4">
       <c r="A14" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" ht="13.5" spans="1:4">
       <c r="A15" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" ht="13.5" spans="1:4">
       <c r="A16" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" ht="13.5" spans="1:4">
       <c r="A17" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" ht="13.5" spans="1:4">
       <c r="A18" s="6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" ht="13.5" spans="1:4">
       <c r="A19" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" ht="13.5" spans="1:4">
       <c r="A20" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" ht="13.5" spans="1:4">
       <c r="A21" s="6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="22" ht="13.5" spans="1:4">
       <c r="A22" s="6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="9" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" ht="13.5" spans="1:4">
       <c r="A23" s="6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="9" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24" ht="13.5" spans="1:4">
       <c r="A24" s="6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" ht="13.5" spans="1:4">
       <c r="A25" s="6">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="9" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" ht="13.5" spans="1:4">
       <c r="A26" s="6">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="9" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" ht="27" spans="1:4">
       <c r="A27" s="6">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="9" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" ht="13.5" spans="1:4">
       <c r="A28" s="6">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" ht="13.5" spans="1:4">
       <c r="A29" s="6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" ht="13.5" spans="1:4">
       <c r="A30" s="6">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="9" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" ht="13.5" spans="1:4">
-      <c r="A31">
-        <v>34</v>
+      <c r="A31" s="6">
+        <v>30</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -6425,11 +6489,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:4">
@@ -6437,11 +6501,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="9" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:4">
@@ -6449,11 +6513,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" ht="13.5" spans="1:4">
@@ -6461,11 +6525,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="9" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="1:4">
@@ -6473,11 +6537,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="9" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" ht="13.5" spans="1:4">
@@ -6485,11 +6549,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="9" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" ht="13.5" spans="1:4">
@@ -6497,11 +6561,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="9" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" ht="13.5" spans="1:4">
@@ -6509,11 +6573,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" ht="13.5" spans="1:4">
@@ -6521,11 +6585,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="9" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" ht="13.5" spans="1:4">
@@ -6533,11 +6597,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="9" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" ht="13.5" spans="1:4">
@@ -6545,11 +6609,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="9" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" ht="13.5" spans="1:4">
@@ -6557,11 +6621,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:4">
@@ -6569,11 +6633,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="9" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" ht="13.5" spans="1:4">
@@ -6581,11 +6645,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" ht="13.5" spans="1:4">
@@ -6593,11 +6657,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" ht="13.5" spans="1:4">
@@ -6605,11 +6669,11 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="9" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" ht="13.5" spans="1:4">
@@ -6617,11 +6681,11 @@
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" ht="13.5" spans="1:4">
@@ -6629,11 +6693,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="20" ht="13.5" spans="1:4">
@@ -6641,11 +6705,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="21" ht="13.5" spans="1:4">
@@ -6653,11 +6717,11 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="9" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="22" ht="13.5" spans="1:4">
@@ -6665,11 +6729,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="9" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="23" ht="13.5" spans="1:4">
@@ -6677,11 +6741,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="9" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -6703,47 +6767,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/python/release_02_1/input/关键字-CAPL函数映射表0125.xlsx
+++ b/python/release_02_1/input/关键字-CAPL函数映射表0125.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="HIL用例关键字说明" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="关键字变更记录" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EM_CAN&amp;Uart&amp;LIN'!$A$1:$Q$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EM_CAN&amp;Uart&amp;LIN'!$A$1:$Q$140</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="518">
   <si>
     <t>编号</t>
   </si>
@@ -304,6 +304,18 @@
     <t>g_HIL_XCP_Swc_Disable_XCP</t>
   </si>
   <si>
+    <t>Enable_ECUSecOC</t>
+  </si>
+  <si>
+    <t>g_HIL_CAN_Swc_Enable_ECUSecOC</t>
+  </si>
+  <si>
+    <t>Disable_ECUSecOC</t>
+  </si>
+  <si>
+    <t>g_HIL_CAN_Swc_Disable_ECUSecOC</t>
+  </si>
+  <si>
     <t>TC_CANTest</t>
   </si>
   <si>
@@ -676,10 +688,7 @@
     <t>g_EM_UDS_ETH_Swc_DOIP</t>
   </si>
   <si>
-    <t>DOIP SA_01_02</t>
-  </si>
-  <si>
-    <t>g_EM_UDS_ETH_Swc_DOIP_SA_01_02</t>
+    <t>DOIP Diag</t>
   </si>
   <si>
     <t>DOIP DiagInterfaceState</t>
@@ -1574,6 +1583,12 @@
   </si>
   <si>
     <t>9.&lt;EM_总线测试专用&gt;中增加DOIP Disconnect关键字</t>
+  </si>
+  <si>
+    <t>10.&lt;HIL用例关键字说明&gt;中增加Enable_XCP、Disable_XCP关键字</t>
+  </si>
+  <si>
+    <t>11.&lt;HIL用例关键字说明&gt;中增加Enable_ECUSecOC、Disable_ECUSecOC关键字</t>
   </si>
 </sst>
 </file>
@@ -2455,7 +2470,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2504,6 +2519,9 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2585,6 +2603,12 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2624,17 +2648,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2700,7 +2718,7 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="0">
-    <open main="155" threadCnt="1"/>
+    <open main="187" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="0" sheetStid="2">
         <open main="1" threadCnt="1"/>
@@ -2992,7 +3010,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3011,7 +3029,7 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="46" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
@@ -3019,543 +3037,569 @@
       </c>
     </row>
     <row r="2" ht="13.5" spans="1:5">
-      <c r="A2" s="44">
+      <c r="A2" s="47">
         <v>1</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47" t="s">
+      <c r="C2" s="49"/>
+      <c r="D2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="49"/>
+      <c r="E2" s="52"/>
     </row>
     <row r="3" ht="13.5" spans="1:5">
-      <c r="A3" s="44">
+      <c r="A3" s="47">
         <v>2</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="49"/>
+      <c r="E3" s="52"/>
     </row>
     <row r="4" ht="13.5" spans="1:5">
-      <c r="A4" s="44">
+      <c r="A4" s="47">
         <v>3</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="47" t="s">
+      <c r="C4" s="49"/>
+      <c r="D4" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="46"/>
+      <c r="E4" s="49"/>
     </row>
     <row r="5" ht="13.5" spans="1:5">
-      <c r="A5" s="44">
+      <c r="A5" s="47">
         <v>4</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="47" t="s">
+      <c r="C5" s="49"/>
+      <c r="D5" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="46"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" ht="13.5" spans="1:5">
-      <c r="A6" s="44">
+      <c r="A6" s="47">
         <v>5</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="47" t="s">
+      <c r="C6" s="49"/>
+      <c r="D6" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="49"/>
+      <c r="E6" s="52"/>
     </row>
     <row r="7" ht="13.5" spans="1:5">
-      <c r="A7" s="44">
+      <c r="A7" s="47">
         <v>6</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47" t="s">
+      <c r="C7" s="49"/>
+      <c r="D7" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="49"/>
+      <c r="E7" s="52"/>
     </row>
     <row r="8" ht="13.5" spans="1:5">
-      <c r="A8" s="44">
+      <c r="A8" s="47">
         <v>7</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="47" t="s">
+      <c r="C8" s="49"/>
+      <c r="D8" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="46"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" ht="13.5" spans="1:5">
-      <c r="A9" s="44">
+      <c r="A9" s="47">
         <v>8</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="47" t="s">
+      <c r="C9" s="49"/>
+      <c r="D9" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="46"/>
+      <c r="E9" s="49"/>
     </row>
     <row r="10" ht="13.5" spans="1:5">
-      <c r="A10" s="44">
+      <c r="A10" s="47">
         <v>9</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="47" t="s">
+      <c r="C10" s="49"/>
+      <c r="D10" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="46"/>
+      <c r="E10" s="49"/>
     </row>
     <row r="11" ht="13.5" spans="1:5">
-      <c r="A11" s="44">
+      <c r="A11" s="47">
         <v>10</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="47" t="s">
+      <c r="C11" s="49"/>
+      <c r="D11" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="46"/>
+      <c r="E11" s="49"/>
     </row>
     <row r="12" ht="13.5" spans="1:5">
-      <c r="A12" s="44">
+      <c r="A12" s="47">
         <v>11</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="47" t="s">
+      <c r="C12" s="49"/>
+      <c r="D12" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="46"/>
+      <c r="E12" s="49"/>
     </row>
     <row r="13" ht="13.5" spans="1:5">
-      <c r="A13" s="44">
+      <c r="A13" s="47">
         <v>12</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="47" t="s">
+      <c r="C13" s="49"/>
+      <c r="D13" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="49" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:5">
-      <c r="A14" s="44">
+      <c r="A14" s="47">
         <v>13</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="47" t="s">
+      <c r="C14" s="49"/>
+      <c r="D14" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="49" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" ht="13.5" spans="1:5">
-      <c r="A15" s="44">
+      <c r="A15" s="47">
         <v>14</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="47" t="s">
+      <c r="C15" s="49"/>
+      <c r="D15" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="46"/>
+      <c r="E15" s="49"/>
     </row>
     <row r="16" ht="13.5" spans="1:5">
-      <c r="A16" s="44">
+      <c r="A16" s="47">
         <v>15</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="47" t="s">
+      <c r="C16" s="49"/>
+      <c r="D16" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="46"/>
+      <c r="E16" s="49"/>
     </row>
     <row r="17" ht="13.5" spans="1:5">
-      <c r="A17" s="44">
+      <c r="A17" s="47">
         <v>16</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="47" t="s">
+      <c r="C17" s="49"/>
+      <c r="D17" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="46"/>
+      <c r="E17" s="49"/>
     </row>
     <row r="18" ht="13.5" spans="1:5">
-      <c r="A18" s="44">
+      <c r="A18" s="47">
         <v>17</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="47" t="s">
+      <c r="C18" s="49"/>
+      <c r="D18" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="46"/>
+      <c r="E18" s="49"/>
     </row>
     <row r="19" ht="13.5" spans="1:5">
-      <c r="A19" s="44">
+      <c r="A19" s="47">
         <v>18</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="47" t="s">
+      <c r="C19" s="49"/>
+      <c r="D19" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="46"/>
+      <c r="E19" s="49"/>
     </row>
     <row r="20" ht="13.5" spans="1:5">
-      <c r="A20" s="44">
+      <c r="A20" s="47">
         <v>19</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="47" t="s">
+      <c r="C20" s="49"/>
+      <c r="D20" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="46"/>
+      <c r="E20" s="49"/>
     </row>
     <row r="21" ht="13.5" spans="1:5">
-      <c r="A21" s="44">
+      <c r="A21" s="47">
         <v>20</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="46"/>
-      <c r="D21" s="47" t="s">
+      <c r="C21" s="49"/>
+      <c r="D21" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="46"/>
+      <c r="E21" s="49"/>
     </row>
     <row r="22" ht="13.5" spans="1:5">
-      <c r="A22" s="44">
+      <c r="A22" s="47">
         <v>21</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="47" t="s">
+      <c r="C22" s="49"/>
+      <c r="D22" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="46"/>
+      <c r="E22" s="49"/>
     </row>
     <row r="23" ht="13.5" spans="1:5">
-      <c r="A23" s="44">
+      <c r="A23" s="47">
         <v>22</v>
       </c>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="47" t="s">
+      <c r="C23" s="49"/>
+      <c r="D23" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="46"/>
+      <c r="E23" s="49"/>
     </row>
     <row r="24" ht="13.5" spans="1:5">
-      <c r="A24" s="44">
+      <c r="A24" s="47">
         <v>23</v>
       </c>
-      <c r="B24" s="48" t="s">
+      <c r="B24" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="47" t="s">
+      <c r="C24" s="49"/>
+      <c r="D24" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="46"/>
+      <c r="E24" s="49"/>
     </row>
     <row r="25" ht="13.5" spans="1:5">
-      <c r="A25" s="44">
+      <c r="A25" s="47">
         <v>24</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B25" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="47" t="s">
+      <c r="C25" s="49"/>
+      <c r="D25" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="46"/>
+      <c r="E25" s="49"/>
     </row>
     <row r="26" ht="13.5" spans="1:5">
-      <c r="A26" s="44">
+      <c r="A26" s="47">
         <v>25</v>
       </c>
-      <c r="B26" s="48" t="s">
+      <c r="B26" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="47" t="s">
+      <c r="C26" s="49"/>
+      <c r="D26" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="46"/>
+      <c r="E26" s="49"/>
     </row>
     <row r="27" ht="13.5" spans="1:5">
-      <c r="A27" s="44">
+      <c r="A27" s="47">
         <v>26</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="47" t="s">
+      <c r="C27" s="49"/>
+      <c r="D27" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="46"/>
+      <c r="E27" s="49"/>
     </row>
     <row r="28" ht="19" customHeight="1" spans="1:5">
-      <c r="A28" s="44">
+      <c r="A28" s="47">
         <v>27</v>
       </c>
-      <c r="B28" s="48" t="s">
+      <c r="B28" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="47" t="s">
+      <c r="C28" s="49"/>
+      <c r="D28" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="46"/>
+      <c r="E28" s="49"/>
     </row>
     <row r="29" ht="19" customHeight="1" spans="1:5">
-      <c r="A29" s="44">
+      <c r="A29" s="47">
         <v>28</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="46"/>
-      <c r="D29" s="47" t="s">
+      <c r="C29" s="49"/>
+      <c r="D29" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="46"/>
+      <c r="E29" s="49"/>
     </row>
     <row r="30" ht="19" customHeight="1" spans="1:5">
-      <c r="A30" s="44">
+      <c r="A30" s="47">
         <v>29</v>
       </c>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="47" t="s">
+      <c r="C30" s="49"/>
+      <c r="D30" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="46"/>
+      <c r="E30" s="49"/>
     </row>
     <row r="31" ht="13.5" spans="1:5">
-      <c r="A31" s="44">
+      <c r="A31" s="47">
         <v>30</v>
       </c>
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="46"/>
-      <c r="D31" s="47" t="s">
+      <c r="C31" s="49"/>
+      <c r="D31" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="46"/>
+      <c r="E31" s="49"/>
     </row>
     <row r="32" ht="13.5" spans="1:5">
-      <c r="A32" s="44">
+      <c r="A32" s="47">
         <v>31</v>
       </c>
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="46"/>
-      <c r="D32" s="47" t="s">
+      <c r="C32" s="49"/>
+      <c r="D32" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="46"/>
+      <c r="E32" s="49"/>
     </row>
     <row r="33" ht="13.5" spans="1:5">
-      <c r="A33" s="44">
+      <c r="A33" s="47">
         <v>32</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="46"/>
-      <c r="D33" s="47" t="s">
+      <c r="C33" s="49"/>
+      <c r="D33" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="46"/>
+      <c r="E33" s="49"/>
     </row>
     <row r="34" ht="13.5" spans="1:5">
-      <c r="A34" s="44">
+      <c r="A34" s="47">
         <v>33</v>
       </c>
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="46"/>
-      <c r="D34" s="47" t="s">
+      <c r="C34" s="49"/>
+      <c r="D34" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="46"/>
+      <c r="E34" s="49"/>
     </row>
     <row r="35" ht="13.5" spans="1:5">
-      <c r="A35" s="44">
+      <c r="A35" s="47">
         <v>34</v>
       </c>
-      <c r="B35" s="48" t="s">
+      <c r="B35" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="47" t="s">
+      <c r="C35" s="49"/>
+      <c r="D35" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="46"/>
+      <c r="E35" s="49"/>
     </row>
     <row r="36" ht="13.5" spans="1:5">
-      <c r="A36" s="44">
+      <c r="A36" s="47">
         <v>35</v>
       </c>
-      <c r="B36" s="48" t="s">
+      <c r="B36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="47" t="s">
+      <c r="C36" s="49"/>
+      <c r="D36" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="E36" s="46"/>
+      <c r="E36" s="49"/>
     </row>
     <row r="37" ht="13.5" spans="1:5">
-      <c r="A37" s="50">
+      <c r="A37" s="53">
         <v>36</v>
       </c>
-      <c r="B37" s="48" t="s">
+      <c r="B37" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="46"/>
-      <c r="D37" s="47" t="s">
+      <c r="C37" s="49"/>
+      <c r="D37" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E37" s="46"/>
+      <c r="E37" s="49"/>
     </row>
     <row r="38" ht="76.5" spans="1:5">
-      <c r="A38" s="51">
+      <c r="A38" s="54">
         <v>37</v>
       </c>
-      <c r="B38" s="52" t="s">
+      <c r="B38" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46" t="s">
+      <c r="C38" s="49"/>
+      <c r="D38" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="E38" s="49" t="s">
+      <c r="E38" s="52" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="53">
+      <c r="A39" s="56">
         <v>38</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55" t="s">
+      <c r="C39" s="58"/>
+      <c r="D39" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="E39" s="55"/>
+      <c r="E39" s="58"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="56">
+      <c r="A40" s="49">
         <v>39</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="46"/>
-      <c r="D40" s="58" t="s">
+      <c r="C40" s="49"/>
+      <c r="D40" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="E40" s="46"/>
+      <c r="E40" s="49"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="56">
+      <c r="A41" s="49">
         <v>40</v>
       </c>
       <c r="B41" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="56"/>
-      <c r="D41" s="58" t="s">
+      <c r="C41" s="49"/>
+      <c r="D41" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="E41" s="56"/>
+      <c r="E41" s="49"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="56">
+      <c r="A42" s="49">
         <v>41</v>
       </c>
       <c r="B42" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="56"/>
-      <c r="D42" s="58" t="s">
+      <c r="C42" s="49"/>
+      <c r="D42" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="E42" s="56"/>
+      <c r="E42" s="49"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="49"/>
+      <c r="D43" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="49"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="49"/>
+      <c r="D44" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" s="49"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -3570,7 +3614,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3593,7 +3637,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3601,1968 +3645,1982 @@
       <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>91</v>
+      <c r="B2" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:4">
       <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>93</v>
+      <c r="B3" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:4">
       <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>94</v>
+      <c r="B4" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>98</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" ht="13.5" spans="1:4">
       <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>97</v>
+      <c r="B5" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="1:4">
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>98</v>
+      <c r="B6" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>102</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" ht="13.5" spans="1:4">
       <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>100</v>
+      <c r="B7" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>104</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" ht="13.5" spans="1:4">
       <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>102</v>
+      <c r="B8" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>106</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="13.5" spans="1:4">
       <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>104</v>
+      <c r="B9" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>108</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" ht="13.5" spans="1:4">
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>106</v>
+      <c r="B10" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>110</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="13.5" spans="1:4">
       <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>109</v>
+      <c r="B11" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="12" ht="13.5" spans="1:4">
       <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>110</v>
+      <c r="B12" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>114</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" ht="13.5" spans="1:4">
       <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>113</v>
+      <c r="B13" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:4">
       <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>114</v>
+      <c r="B14" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>118</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" ht="13.5" spans="1:4">
       <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>116</v>
+      <c r="B15" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>120</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" ht="13.5" spans="1:4">
       <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>118</v>
+      <c r="B16" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>122</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" ht="13.5" spans="1:5">
       <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="B17" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="29"/>
+        <v>124</v>
+      </c>
+      <c r="E17" s="30"/>
     </row>
     <row r="18" ht="13.5" spans="1:4">
       <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>121</v>
+      <c r="B18" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" ht="13.5" spans="1:5">
       <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>123</v>
+      <c r="B19" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>127</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" s="29"/>
+        <v>128</v>
+      </c>
+      <c r="E19" s="30"/>
     </row>
     <row r="20" ht="13.5" spans="1:5">
       <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>125</v>
+      <c r="B20" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>129</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="29"/>
+        <v>130</v>
+      </c>
+      <c r="E20" s="30"/>
     </row>
     <row r="21" ht="13.5" spans="1:5">
       <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>127</v>
+      <c r="B21" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>131</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" s="29"/>
+        <v>132</v>
+      </c>
+      <c r="E21" s="30"/>
     </row>
     <row r="22" ht="13.5" spans="1:4">
       <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>129</v>
+      <c r="B22" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>133</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" ht="13.5" spans="1:4">
       <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>131</v>
+      <c r="B23" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>135</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" ht="13.5" spans="1:4">
       <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>133</v>
+      <c r="B24" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>137</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" ht="13.5" spans="1:4">
       <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>135</v>
+      <c r="B25" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>139</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" ht="13.5" spans="1:4">
       <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>137</v>
+      <c r="B26" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>141</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" ht="13.5" spans="1:4">
       <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>139</v>
+      <c r="B27" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>143</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" ht="13.5" spans="1:4">
       <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>141</v>
+      <c r="B28" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>145</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" ht="13.5" spans="1:4">
       <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>143</v>
+      <c r="B29" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>147</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" ht="13.5" spans="1:4">
       <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="27" t="s">
-        <v>145</v>
+      <c r="B30" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>149</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" ht="13.5" spans="1:4">
       <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>147</v>
+      <c r="B31" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>151</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" ht="13.5" spans="1:4">
       <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>149</v>
+      <c r="B32" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>153</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" ht="13.5" spans="1:4">
       <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>151</v>
+      <c r="B33" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>155</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" ht="13.5" spans="1:4">
       <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>153</v>
+      <c r="B34" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>157</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" ht="13.5" spans="1:4">
       <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>155</v>
+      <c r="B35" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>159</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" ht="13.5" spans="1:4">
       <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="27" t="s">
-        <v>157</v>
+      <c r="B36" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>161</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" ht="13.5" spans="1:4">
       <c r="A37" s="6">
         <v>36</v>
       </c>
-      <c r="B37" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>159</v>
+      <c r="B37" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>163</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" ht="13.5" spans="1:4">
       <c r="A38" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>161</v>
+      <c r="B38" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>165</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" ht="13.5" spans="1:4">
       <c r="A39" s="6">
         <v>38</v>
       </c>
-      <c r="B39" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>163</v>
+      <c r="B39" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>167</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" ht="13.5" spans="1:4">
       <c r="A40" s="6">
         <v>39</v>
       </c>
-      <c r="B40" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>165</v>
+      <c r="B40" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>169</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" ht="13.5" spans="1:4">
       <c r="A41" s="6">
         <v>40</v>
       </c>
-      <c r="B41" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="27" t="s">
-        <v>167</v>
+      <c r="B41" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>171</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" ht="13.5" spans="1:4">
       <c r="A42" s="6">
         <v>41</v>
       </c>
-      <c r="B42" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="27" t="s">
-        <v>169</v>
+      <c r="B42" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>173</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" ht="13.5" spans="1:4">
       <c r="A43" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>171</v>
+      <c r="B43" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>175</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" ht="13.5" spans="1:4">
       <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>173</v>
+      <c r="B44" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>177</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" ht="13.5" spans="1:4">
       <c r="A45" s="6">
         <v>44</v>
       </c>
-      <c r="B45" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>175</v>
+      <c r="B45" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" ht="13.5" spans="1:4">
       <c r="A46" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>177</v>
+      <c r="B46" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>181</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" ht="13.5" spans="1:4">
       <c r="A47" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" s="31" t="s">
-        <v>179</v>
+      <c r="B47" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>183</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" ht="13.5" spans="1:4">
       <c r="A48" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>181</v>
+      <c r="B48" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>185</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" ht="13.5" spans="1:5">
       <c r="A49" s="6">
         <v>48</v>
       </c>
-      <c r="B49" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>183</v>
+      <c r="B49" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="E49" s="25"/>
+        <v>188</v>
+      </c>
+      <c r="E49" s="26"/>
     </row>
     <row r="50" ht="13.5" spans="1:4">
       <c r="A50" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C50" s="31" t="s">
-        <v>185</v>
+      <c r="B50" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" ht="13.5" spans="1:4">
       <c r="A51" s="6">
         <v>50</v>
       </c>
-      <c r="B51" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" s="31" t="s">
-        <v>187</v>
+      <c r="B51" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>191</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" ht="13.5" spans="1:4">
       <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" s="31" t="s">
-        <v>189</v>
+      <c r="B52" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>193</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53" ht="13.5" spans="1:4">
       <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C53" s="31" t="s">
-        <v>191</v>
+      <c r="B53" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>195</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" ht="13.5" spans="1:4">
       <c r="A54" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" s="31" t="s">
-        <v>193</v>
+      <c r="B54" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>197</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" ht="13.5" spans="1:4">
       <c r="A55" s="6">
         <v>54</v>
       </c>
-      <c r="B55" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" s="31" t="s">
-        <v>195</v>
+      <c r="B55" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>199</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" ht="13.5" spans="1:4">
       <c r="A56" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" s="31" t="s">
-        <v>197</v>
+      <c r="B56" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>201</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" ht="13.5" spans="1:4">
       <c r="A57" s="6">
         <v>56</v>
       </c>
-      <c r="B57" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" s="31" t="s">
-        <v>199</v>
+      <c r="B57" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>203</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58" ht="13.5" spans="1:4">
       <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" s="31" t="s">
-        <v>201</v>
+      <c r="B58" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>205</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" ht="13.5" spans="1:4">
       <c r="A59" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C59" s="32" t="s">
-        <v>203</v>
+      <c r="B59" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>207</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" ht="13.5" spans="1:4">
       <c r="A60" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" s="32" t="s">
-        <v>205</v>
+      <c r="B60" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>209</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" ht="13.5" spans="1:4">
       <c r="A61" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C61" s="31" t="s">
-        <v>207</v>
+      <c r="B61" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C61" s="32" t="s">
+        <v>211</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" ht="13.5" spans="1:4">
       <c r="A62" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="26" t="s">
-        <v>89</v>
+      <c r="B62" s="27" t="s">
+        <v>93</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" ht="13.5" spans="1:4">
       <c r="A63" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="26" t="s">
-        <v>89</v>
+      <c r="B63" s="27" t="s">
+        <v>93</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" ht="13.5" spans="1:4">
       <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>213</v>
+      <c r="B64" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>217</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" ht="13.5" spans="1:4">
       <c r="A65" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="26" t="s">
-        <v>89</v>
+      <c r="B65" s="27" t="s">
+        <v>93</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" ht="13.5" spans="1:4">
       <c r="A66" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="26" t="s">
-        <v>89</v>
+      <c r="B66" s="27" t="s">
+        <v>93</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="67" ht="13.5" spans="1:4">
       <c r="A67" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="26" t="s">
-        <v>89</v>
+      <c r="B67" s="27" t="s">
+        <v>93</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" ht="13.5" spans="1:4">
       <c r="A68" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C68" s="27" t="s">
-        <v>221</v>
+      <c r="B68" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>224</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" ht="13.5" spans="1:4">
       <c r="A69" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" s="31" t="s">
-        <v>223</v>
+      <c r="B69" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="32" t="s">
+        <v>226</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" ht="13.5" spans="1:4">
       <c r="A70" s="6">
         <v>69</v>
       </c>
-      <c r="B70" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="31" t="s">
-        <v>225</v>
+      <c r="B70" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>228</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="71" ht="27" spans="1:4">
       <c r="A71" s="6">
         <v>70</v>
       </c>
-      <c r="B71" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="C71" s="31" t="s">
-        <v>227</v>
+      <c r="B71" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="C71" s="32" t="s">
+        <v>230</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72" ht="13.5" spans="1:4">
       <c r="A72" s="6">
         <v>71</v>
       </c>
-      <c r="B72" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C72" s="34" t="s">
-        <v>229</v>
+      <c r="B72" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72" s="35" t="s">
+        <v>232</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" ht="13.5" spans="1:4">
       <c r="A73" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>231</v>
+      <c r="B73" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C73" s="35" t="s">
+        <v>234</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74" ht="13.5" spans="1:4">
       <c r="A74" s="6">
         <v>73</v>
       </c>
-      <c r="B74" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="34" t="s">
-        <v>233</v>
+      <c r="B74" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74" s="35" t="s">
+        <v>236</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" ht="13.5" spans="1:4">
       <c r="A75" s="6">
         <v>74</v>
       </c>
-      <c r="B75" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" s="34" t="s">
-        <v>235</v>
+      <c r="B75" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="35" t="s">
+        <v>238</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" ht="13.5" spans="1:4">
       <c r="A76" s="6">
         <v>75</v>
       </c>
-      <c r="B76" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C76" s="34" t="s">
-        <v>237</v>
+      <c r="B76" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>240</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="77" ht="13.5" spans="1:4">
       <c r="A77" s="6">
         <v>76</v>
       </c>
-      <c r="B77" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C77" s="34" t="s">
-        <v>239</v>
+      <c r="B77" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C77" s="35" t="s">
+        <v>242</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" ht="13.5" spans="1:4">
       <c r="A78" s="6">
         <v>77</v>
       </c>
-      <c r="B78" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C78" s="35" t="s">
-        <v>241</v>
+      <c r="B78" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="36" t="s">
+        <v>244</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="79" ht="13.5" spans="1:4">
       <c r="A79" s="6">
         <v>78</v>
       </c>
-      <c r="B79" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" s="35" t="s">
-        <v>243</v>
+      <c r="B79" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" s="36" t="s">
+        <v>246</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="80" ht="13.5" spans="1:4">
       <c r="A80" s="6">
         <v>79</v>
       </c>
-      <c r="B80" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" s="35" t="s">
-        <v>245</v>
+      <c r="B80" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C80" s="36" t="s">
+        <v>248</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="81" ht="13.5" spans="1:4">
       <c r="A81" s="6">
         <v>80</v>
       </c>
-      <c r="B81" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="35" t="s">
-        <v>247</v>
+      <c r="B81" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>250</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="82" ht="13.5" spans="1:4">
       <c r="A82" s="6">
         <v>81</v>
       </c>
-      <c r="B82" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C82" s="35" t="s">
-        <v>249</v>
+      <c r="B82" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C82" s="36" t="s">
+        <v>252</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" ht="13.5" spans="1:4">
       <c r="A83" s="6">
         <v>82</v>
       </c>
-      <c r="B83" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C83" s="35" t="s">
-        <v>251</v>
+      <c r="B83" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C83" s="36" t="s">
+        <v>254</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" ht="13.5" spans="1:4">
       <c r="A84" s="6">
         <v>83</v>
       </c>
-      <c r="B84" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C84" s="35" t="s">
-        <v>253</v>
+      <c r="B84" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" s="36" t="s">
+        <v>256</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="85" ht="13.5" spans="1:4">
       <c r="A85" s="6">
         <v>84</v>
       </c>
-      <c r="B85" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C85" s="35" t="s">
-        <v>255</v>
+      <c r="B85" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" s="36" t="s">
+        <v>258</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="86" ht="13.5" spans="1:4">
       <c r="A86" s="6">
         <v>85</v>
       </c>
-      <c r="B86" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C86" s="35" t="s">
-        <v>257</v>
+      <c r="B86" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C86" s="36" t="s">
+        <v>260</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" ht="13.5" spans="1:4">
       <c r="A87" s="6">
         <v>86</v>
       </c>
-      <c r="B87" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C87" s="34" t="s">
-        <v>259</v>
+      <c r="B87" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" s="35" t="s">
+        <v>262</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="88" ht="13.5" spans="1:4">
       <c r="A88" s="6">
         <v>87</v>
       </c>
-      <c r="B88" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" s="34" t="s">
-        <v>261</v>
+      <c r="B88" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C88" s="35" t="s">
+        <v>264</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="89" ht="13.5" spans="1:4">
       <c r="A89" s="6">
         <v>88</v>
       </c>
-      <c r="B89" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C89" s="34" t="s">
-        <v>263</v>
+      <c r="B89" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C89" s="35" t="s">
+        <v>266</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90" ht="13.5" spans="1:4">
       <c r="A90" s="6">
         <v>89</v>
       </c>
-      <c r="B90" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C90" s="34" t="s">
-        <v>265</v>
+      <c r="B90" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C90" s="35" t="s">
+        <v>268</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" ht="13.5" spans="1:4">
       <c r="A91" s="6">
         <v>90</v>
       </c>
-      <c r="B91" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C91" s="34" t="s">
-        <v>267</v>
+      <c r="B91" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C91" s="35" t="s">
+        <v>270</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="92" ht="13.5" spans="1:4">
       <c r="A92" s="6">
         <v>91</v>
       </c>
-      <c r="B92" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C92" s="34" t="s">
-        <v>269</v>
+      <c r="B92" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C92" s="35" t="s">
+        <v>272</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="93" ht="13.5" spans="1:4">
       <c r="A93" s="6">
         <v>92</v>
       </c>
-      <c r="B93" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C93" s="34" t="s">
-        <v>271</v>
+      <c r="B93" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C93" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" ht="13.5" spans="1:4">
       <c r="A94" s="6">
         <v>93</v>
       </c>
-      <c r="B94" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C94" s="34" t="s">
-        <v>273</v>
+      <c r="B94" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C94" s="35" t="s">
+        <v>276</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="95" ht="13.5" spans="1:4">
       <c r="A95" s="6">
         <v>94</v>
       </c>
-      <c r="B95" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C95" s="34" t="s">
-        <v>275</v>
+      <c r="B95" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C95" s="35" t="s">
+        <v>278</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="96" ht="13.5" spans="1:4">
       <c r="A96" s="6">
         <v>95</v>
       </c>
-      <c r="B96" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C96" s="34" t="s">
-        <v>277</v>
+      <c r="B96" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C96" s="35" t="s">
+        <v>280</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="97" ht="13.5" spans="1:4">
       <c r="A97" s="6">
         <v>96</v>
       </c>
-      <c r="B97" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C97" s="35" t="s">
-        <v>279</v>
+      <c r="B97" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C97" s="36" t="s">
+        <v>282</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="98" ht="13.5" spans="1:4">
       <c r="A98" s="6">
         <v>97</v>
       </c>
-      <c r="B98" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C98" s="35" t="s">
-        <v>281</v>
+      <c r="B98" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C98" s="36" t="s">
+        <v>284</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="99" ht="13.5" spans="1:4">
       <c r="A99" s="6">
         <v>98</v>
       </c>
-      <c r="B99" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C99" s="35" t="s">
-        <v>283</v>
+      <c r="B99" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C99" s="36" t="s">
+        <v>286</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="100" ht="13.5" spans="1:4">
       <c r="A100" s="6">
         <v>99</v>
       </c>
-      <c r="B100" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C100" s="35" t="s">
-        <v>285</v>
+      <c r="B100" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C100" s="36" t="s">
+        <v>288</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="101" ht="13.5" spans="1:4">
       <c r="A101" s="6">
         <v>100</v>
       </c>
-      <c r="B101" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C101" s="35" t="s">
-        <v>287</v>
+      <c r="B101" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C101" s="36" t="s">
+        <v>290</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="102" ht="13.5" spans="1:4">
       <c r="A102" s="6">
         <v>101</v>
       </c>
-      <c r="B102" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C102" s="35" t="s">
-        <v>289</v>
+      <c r="B102" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C102" s="36" t="s">
+        <v>292</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="103" ht="13.5" spans="1:4">
       <c r="A103" s="6">
         <v>102</v>
       </c>
-      <c r="B103" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C103" s="35" t="s">
-        <v>291</v>
+      <c r="B103" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C103" s="36" t="s">
+        <v>294</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104" ht="13.5" spans="1:4">
       <c r="A104" s="6">
         <v>103</v>
       </c>
-      <c r="B104" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C104" s="35" t="s">
-        <v>293</v>
+      <c r="B104" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C104" s="36" t="s">
+        <v>296</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="105" ht="13.5" spans="1:4">
       <c r="A105" s="6">
         <v>104</v>
       </c>
-      <c r="B105" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C105" s="35" t="s">
-        <v>295</v>
+      <c r="B105" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C105" s="36" t="s">
+        <v>298</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="106" ht="13.5" spans="1:4">
       <c r="A106" s="6">
         <v>105</v>
       </c>
-      <c r="B106" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C106" s="35" t="s">
-        <v>297</v>
+      <c r="B106" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C106" s="36" t="s">
+        <v>300</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="107" ht="13.5" spans="1:4">
       <c r="A107" s="6">
         <v>106</v>
       </c>
-      <c r="B107" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C107" s="36" t="s">
-        <v>300</v>
+      <c r="B107" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C107" s="37" t="s">
+        <v>303</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="108" ht="13.5" spans="1:4">
       <c r="A108" s="6">
         <v>107</v>
       </c>
-      <c r="B108" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C108" s="36" t="s">
+      <c r="B108" s="27" t="s">
         <v>302</v>
       </c>
+      <c r="C108" s="37" t="s">
+        <v>305</v>
+      </c>
       <c r="D108" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="109" ht="13.5" spans="1:4">
       <c r="A109" s="6">
         <v>108</v>
       </c>
-      <c r="B109" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C109" s="36" t="s">
-        <v>304</v>
+      <c r="B109" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C109" s="37" t="s">
+        <v>307</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="110" ht="13.5" spans="1:4">
       <c r="A110" s="6">
         <v>109</v>
       </c>
-      <c r="B110" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C110" s="36" t="s">
-        <v>306</v>
+      <c r="B110" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" s="37" t="s">
+        <v>309</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="111" ht="13.5" spans="1:6">
       <c r="A111" s="6">
         <v>110</v>
       </c>
-      <c r="B111" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C111" s="36" t="s">
-        <v>308</v>
+      <c r="B111" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C111" s="37" t="s">
+        <v>311</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E111" s="38"/>
-      <c r="F111" s="39"/>
+        <v>312</v>
+      </c>
+      <c r="E111" s="39"/>
+      <c r="F111" s="40"/>
     </row>
     <row r="112" ht="13.5" spans="1:6">
       <c r="A112" s="6">
         <v>111</v>
       </c>
-      <c r="B112" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C112" s="36" t="s">
-        <v>310</v>
+      <c r="B112" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C112" s="37" t="s">
+        <v>313</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="E112" s="38"/>
-      <c r="F112" s="39"/>
+        <v>314</v>
+      </c>
+      <c r="E112" s="39"/>
+      <c r="F112" s="40"/>
     </row>
     <row r="113" ht="13.5" spans="1:6">
       <c r="A113" s="6">
         <v>112</v>
       </c>
-      <c r="B113" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C113" s="36" t="s">
-        <v>312</v>
+      <c r="B113" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C113" s="37" t="s">
+        <v>315</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="E113" s="38"/>
-      <c r="F113" s="39"/>
+        <v>316</v>
+      </c>
+      <c r="E113" s="39"/>
+      <c r="F113" s="40"/>
     </row>
     <row r="114" ht="13.5" spans="1:6">
       <c r="A114" s="6">
         <v>113</v>
       </c>
-      <c r="B114" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C114" s="36" t="s">
-        <v>314</v>
+      <c r="B114" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C114" s="37" t="s">
+        <v>317</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="E114" s="38"/>
-      <c r="F114" s="39"/>
+        <v>318</v>
+      </c>
+      <c r="E114" s="39"/>
+      <c r="F114" s="40"/>
     </row>
     <row r="115" ht="13.5" spans="1:6">
       <c r="A115" s="6">
         <v>114</v>
       </c>
-      <c r="B115" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C115" s="37" t="s">
-        <v>316</v>
+      <c r="B115" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C115" s="38" t="s">
+        <v>319</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="E115" s="38"/>
-      <c r="F115" s="38"/>
+        <v>320</v>
+      </c>
+      <c r="E115" s="39"/>
+      <c r="F115" s="39"/>
     </row>
     <row r="116" ht="13.5" spans="1:6">
       <c r="A116" s="6">
         <v>115</v>
       </c>
-      <c r="B116" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C116" s="37" t="s">
-        <v>125</v>
+      <c r="B116" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C116" s="38" t="s">
+        <v>129</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="E116" s="38"/>
-      <c r="F116" s="39"/>
+        <v>321</v>
+      </c>
+      <c r="E116" s="39"/>
+      <c r="F116" s="40"/>
     </row>
     <row r="117" ht="13.5" spans="1:6">
       <c r="A117" s="6">
         <v>116</v>
       </c>
-      <c r="B117" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C117" s="37" t="s">
-        <v>127</v>
+      <c r="B117" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C117" s="38" t="s">
+        <v>131</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="E117" s="38"/>
-      <c r="F117" s="39"/>
+        <v>322</v>
+      </c>
+      <c r="E117" s="39"/>
+      <c r="F117" s="40"/>
     </row>
     <row r="118" ht="13.5" spans="1:6">
       <c r="A118" s="6">
         <v>117</v>
       </c>
-      <c r="B118" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C118" s="37" t="s">
-        <v>320</v>
+      <c r="B118" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C118" s="38" t="s">
+        <v>323</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="E118" s="38"/>
-      <c r="F118" s="39"/>
+        <v>324</v>
+      </c>
+      <c r="E118" s="39"/>
+      <c r="F118" s="40"/>
     </row>
     <row r="119" ht="13.5" spans="1:6">
       <c r="A119" s="6">
         <v>118</v>
       </c>
-      <c r="B119" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C119" s="37" t="s">
-        <v>322</v>
+      <c r="B119" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C119" s="38" t="s">
+        <v>325</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="E119" s="38"/>
-      <c r="F119" s="39"/>
+        <v>326</v>
+      </c>
+      <c r="E119" s="39"/>
+      <c r="F119" s="40"/>
     </row>
     <row r="120" ht="13.5" spans="1:6">
       <c r="A120" s="6">
         <v>119</v>
       </c>
-      <c r="B120" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C120" s="37" t="s">
-        <v>324</v>
+      <c r="B120" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C120" s="38" t="s">
+        <v>327</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E120" s="38"/>
-      <c r="F120" s="39"/>
+        <v>328</v>
+      </c>
+      <c r="E120" s="39"/>
+      <c r="F120" s="40"/>
     </row>
     <row r="121" ht="13.5" spans="1:6">
       <c r="A121" s="6">
         <v>120</v>
       </c>
-      <c r="B121" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C121" s="37" t="s">
-        <v>326</v>
+      <c r="B121" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C121" s="38" t="s">
+        <v>329</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="E121" s="38"/>
-      <c r="F121" s="39"/>
+        <v>330</v>
+      </c>
+      <c r="E121" s="39"/>
+      <c r="F121" s="40"/>
     </row>
     <row r="122" ht="13.5" spans="1:6">
       <c r="A122" s="6">
         <v>121</v>
       </c>
-      <c r="B122" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C122" s="37" t="s">
-        <v>328</v>
+      <c r="B122" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C122" s="38" t="s">
+        <v>331</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="E122" s="38"/>
-      <c r="F122" s="39"/>
+        <v>332</v>
+      </c>
+      <c r="E122" s="39"/>
+      <c r="F122" s="40"/>
     </row>
     <row r="123" ht="13.5" spans="1:6">
       <c r="A123" s="6">
         <v>122</v>
       </c>
-      <c r="B123" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C123" s="36" t="s">
-        <v>330</v>
+      <c r="B123" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C123" s="37" t="s">
+        <v>333</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="E123" s="38"/>
-      <c r="F123" s="38"/>
+        <v>334</v>
+      </c>
+      <c r="E123" s="39"/>
+      <c r="F123" s="39"/>
     </row>
     <row r="124" ht="13.5" spans="1:4">
       <c r="A124" s="6">
         <v>123</v>
       </c>
-      <c r="B124" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C124" s="36" t="s">
-        <v>332</v>
+      <c r="B124" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C124" s="37" t="s">
+        <v>335</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="125" ht="13.5" spans="1:4">
       <c r="A125" s="6">
         <v>124</v>
       </c>
-      <c r="B125" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C125" s="36" t="s">
-        <v>334</v>
+      <c r="B125" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C125" s="37" t="s">
+        <v>337</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="126" ht="13.5" spans="1:4">
       <c r="A126" s="6">
         <v>125</v>
       </c>
-      <c r="B126" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C126" s="36" t="s">
-        <v>336</v>
+      <c r="B126" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C126" s="37" t="s">
+        <v>339</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="127" ht="13.5" spans="1:4">
       <c r="A127" s="6">
         <v>126</v>
       </c>
-      <c r="B127" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C127" s="36" t="s">
-        <v>338</v>
+      <c r="B127" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C127" s="37" t="s">
+        <v>341</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="128" ht="13.5" spans="1:4">
       <c r="A128" s="6">
         <v>127</v>
       </c>
-      <c r="B128" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C128" s="37" t="s">
-        <v>340</v>
+      <c r="B128" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C128" s="38" t="s">
+        <v>343</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="129" ht="13.5" spans="1:4">
       <c r="A129" s="6">
         <v>128</v>
       </c>
-      <c r="B129" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C129" s="37" t="s">
-        <v>342</v>
+      <c r="B129" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C129" s="38" t="s">
+        <v>345</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="130" ht="13.5" spans="1:4">
       <c r="A130" s="6">
         <v>129</v>
       </c>
-      <c r="B130" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C130" s="37" t="s">
-        <v>344</v>
+      <c r="B130" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C130" s="38" t="s">
+        <v>347</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="131" ht="13.5" spans="1:4">
       <c r="A131" s="6">
         <v>130</v>
       </c>
-      <c r="B131" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C131" s="37" t="s">
-        <v>346</v>
+      <c r="B131" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C131" s="38" t="s">
+        <v>349</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" ht="13.5" spans="1:4">
       <c r="A132" s="6">
         <v>131</v>
       </c>
-      <c r="B132" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C132" s="37" t="s">
-        <v>348</v>
+      <c r="B132" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C132" s="38" t="s">
+        <v>351</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="133" ht="13.5" spans="1:4">
       <c r="A133" s="6">
         <v>132</v>
       </c>
-      <c r="B133" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C133" s="37" t="s">
-        <v>350</v>
+      <c r="B133" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C133" s="38" t="s">
+        <v>353</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="134" ht="13.5" spans="1:4">
       <c r="A134" s="6">
         <v>133</v>
       </c>
-      <c r="B134" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C134" s="37" t="s">
-        <v>352</v>
+      <c r="B134" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C134" s="38" t="s">
+        <v>355</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="135" ht="13.5" spans="1:4">
       <c r="A135" s="6">
         <v>134</v>
       </c>
-      <c r="B135" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C135" s="37" t="s">
-        <v>354</v>
+      <c r="B135" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C135" s="38" t="s">
+        <v>357</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="136" ht="27" spans="1:4">
       <c r="A136" s="6">
         <v>135</v>
       </c>
-      <c r="B136" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="C136" s="40" t="s">
-        <v>330</v>
+      <c r="B136" s="34" t="s">
+        <v>359</v>
+      </c>
+      <c r="C136" s="41" t="s">
+        <v>333</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="137" ht="27" spans="1:4">
       <c r="A137" s="6">
         <v>136</v>
       </c>
-      <c r="B137" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="C137" s="17"/>
+      <c r="B137" s="34" t="s">
+        <v>361</v>
+      </c>
+      <c r="C137" s="18"/>
       <c r="D137" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="138" ht="27" spans="1:4">
       <c r="A138" s="6">
         <v>137</v>
       </c>
-      <c r="B138" s="33" t="s">
-        <v>360</v>
-      </c>
-      <c r="C138" s="17"/>
+      <c r="B138" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="C138" s="18"/>
       <c r="D138" s="9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="139" ht="40.5" spans="1:4">
       <c r="A139" s="6">
         <v>138</v>
       </c>
-      <c r="B139" s="41" t="s">
-        <v>362</v>
-      </c>
-      <c r="C139" s="42"/>
+      <c r="B139" s="42" t="s">
+        <v>365</v>
+      </c>
+      <c r="C139" s="43"/>
       <c r="D139" s="9" t="s">
-        <v>363</v>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="140" ht="13.5" spans="1:4">
+      <c r="A140" s="6">
+        <v>139</v>
+      </c>
+      <c r="B140" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C140" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q139" etc:filterBottomFollowUsedRange="1">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q140" etc:filterBottomFollowUsedRange="1">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D1 B138:B139 F124:Q139 D139 C116:D136 G111:Q123 D115 C6:C46 C55:C57 C47:D54 C68:C70 C59:D67 B71:D71 C72:D96 D97 C98:D105 D106 F1:Q110 C107:D114" numberStoredAsText="1"/>
+    <ignoredError sqref="F65:Q110 C65:D67 C107:D114 F1:Q63 D106 C98:D105 D97 C72:D96 B71:D71 C59:D63 C68:C70 C47:D54 C55:C57 C6:C46 D115 G111:Q123 C116:D136 D139 F124:Q139 B138:B139 A1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
   <picture r:id="rId1"/>
 </worksheet>
@@ -5594,7 +5652,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5603,13 +5661,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:4">
@@ -5617,13 +5675,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:5">
@@ -5631,375 +5689,375 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="E4" s="25"/>
+        <v>372</v>
+      </c>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" ht="13.5" spans="1:5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="E5" s="25"/>
+        <v>374</v>
+      </c>
+      <c r="E5" s="26"/>
     </row>
     <row r="6" ht="13.5" spans="1:5">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="E6" s="25"/>
+        <v>376</v>
+      </c>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" ht="13.5" spans="1:5">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="E7" s="25"/>
+        <v>378</v>
+      </c>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" ht="13.5" spans="1:5">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="E8" s="25"/>
+        <v>380</v>
+      </c>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" ht="13.5" spans="1:5">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="E9" s="25"/>
+        <v>382</v>
+      </c>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" ht="13.5" spans="1:5">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="E10" s="25"/>
+        <v>384</v>
+      </c>
+      <c r="E10" s="26"/>
     </row>
     <row r="11" ht="13.5" spans="1:5">
       <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="E11" s="25"/>
+        <v>386</v>
+      </c>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" ht="13.5" spans="1:5">
       <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="E12" s="25"/>
+        <v>388</v>
+      </c>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" ht="13.5" spans="1:5">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="E13" s="25"/>
+        <v>390</v>
+      </c>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" ht="13.5" spans="1:5">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="E14" s="25"/>
+        <v>392</v>
+      </c>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" ht="13.5" spans="1:5">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="E15" s="25"/>
+        <v>394</v>
+      </c>
+      <c r="E15" s="26"/>
     </row>
     <row r="16" ht="13.5" spans="1:5">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>393</v>
-      </c>
-      <c r="E16" s="25"/>
+        <v>395</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="E16" s="26"/>
     </row>
     <row r="17" ht="13.5" spans="1:5">
       <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>394</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>395</v>
-      </c>
-      <c r="E17" s="25"/>
+        <v>397</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="E17" s="26"/>
     </row>
     <row r="18" ht="13.5" spans="1:5">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="E18" s="25"/>
+        <v>399</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" ht="13.5" spans="1:5">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>399</v>
-      </c>
-      <c r="E19" s="25"/>
+        <v>401</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>402</v>
+      </c>
+      <c r="E19" s="26"/>
     </row>
     <row r="20" ht="13.5" spans="1:5">
       <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>401</v>
-      </c>
-      <c r="E20" s="25"/>
+        <v>403</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E20" s="26"/>
     </row>
     <row r="21" ht="13.5" spans="1:5">
       <c r="A21" s="6">
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>403</v>
-      </c>
-      <c r="E21" s="25"/>
+        <v>405</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="E21" s="26"/>
     </row>
     <row r="22" ht="13.5" spans="1:5">
       <c r="A22" s="6">
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>405</v>
-      </c>
-      <c r="E22" s="25"/>
+        <v>407</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="E22" s="26"/>
     </row>
     <row r="23" ht="13.5" spans="1:5">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>406</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>407</v>
-      </c>
-      <c r="E23" s="25"/>
+        <v>409</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="E23" s="26"/>
     </row>
     <row r="24" ht="13.5" spans="1:5">
       <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="E24" s="25"/>
+        <v>411</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>412</v>
+      </c>
+      <c r="E24" s="26"/>
     </row>
     <row r="25" ht="13.5" spans="1:5">
       <c r="A25" s="6">
         <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>411</v>
-      </c>
-      <c r="E25" s="25"/>
+        <v>413</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="E25" s="26"/>
     </row>
     <row r="26" ht="13.5" spans="1:5">
       <c r="A26" s="6">
         <v>25</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="E26" s="25"/>
+        <v>415</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>416</v>
+      </c>
+      <c r="E26" s="26"/>
     </row>
     <row r="27" ht="13.5" spans="1:5">
       <c r="A27" s="6">
         <v>26</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="E27" s="25"/>
+        <v>417</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>418</v>
+      </c>
+      <c r="E27" s="26"/>
     </row>
     <row r="28" ht="13.5" spans="1:5">
       <c r="A28" s="6">
         <v>27</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>416</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="E28" s="25"/>
+        <v>419</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="E28" s="26"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -6014,7 +6072,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6037,7 +6095,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6046,13 +6104,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:4">
@@ -6060,13 +6118,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:4">
@@ -6074,13 +6132,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" ht="13.5" spans="1:4">
@@ -6088,13 +6146,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="1:4">
@@ -6102,13 +6160,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" ht="13.5" spans="1:4">
@@ -6116,13 +6174,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" ht="13.5" spans="1:4">
@@ -6130,13 +6188,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" ht="13.5" spans="1:4">
@@ -6144,13 +6202,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" ht="13.5" spans="1:4">
@@ -6158,13 +6216,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" ht="13.5" spans="1:4">
@@ -6172,13 +6230,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" ht="13.5" spans="1:4">
@@ -6186,13 +6244,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" ht="13.5" spans="1:4">
@@ -6200,13 +6258,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:4">
@@ -6214,13 +6272,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15" ht="13.5" spans="1:4">
@@ -6228,13 +6286,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" ht="13.5" spans="1:4">
@@ -6242,13 +6300,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" ht="13.5" spans="1:4">
@@ -6256,13 +6314,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>213</v>
+        <v>447</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>217</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" ht="13.5" spans="1:4">
@@ -6270,13 +6328,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" ht="13.5" spans="1:4">
@@ -6284,13 +6342,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" ht="13.5" spans="1:4">
@@ -6298,13 +6356,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" ht="13.5" spans="1:4">
@@ -6312,37 +6370,37 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22" ht="13.5" spans="1:4">
       <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>445</v>
-      </c>
-      <c r="C22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="C22" s="18"/>
       <c r="D22" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" ht="13.5" spans="1:4">
       <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="C23" s="17"/>
+      <c r="B23" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="C23" s="18"/>
       <c r="D23" s="9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" ht="13.5" spans="1:4">
@@ -6350,11 +6408,11 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="C24" s="18"/>
+        <v>230</v>
+      </c>
+      <c r="C24" s="19"/>
       <c r="D24" s="9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" ht="13.5" spans="1:4">
@@ -6362,61 +6420,61 @@
         <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="C25" s="18"/>
+        <v>450</v>
+      </c>
+      <c r="C25" s="19"/>
       <c r="D25" s="9" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="26" ht="13.5" spans="1:4">
       <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="C26" s="18"/>
+      <c r="B26" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="C26" s="19"/>
       <c r="D26" s="9" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27" ht="27" spans="1:4">
       <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="C27" s="18"/>
+      <c r="B27" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="C27" s="19"/>
       <c r="D27" s="9" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" ht="13.5" spans="1:4">
       <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>183</v>
+      <c r="B28" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>187</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="29" ht="13.5" spans="1:4">
       <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>455</v>
+      <c r="B29" s="20" t="s">
+        <v>458</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="30" ht="13.5" spans="1:4">
@@ -6424,25 +6482,39 @@
         <v>29</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="9" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="31" ht="13.5" spans="1:4">
       <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>89</v>
+      <c r="B31" s="22" t="s">
+        <v>93</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>460</v>
+        <v>462</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="32" ht="13.5" spans="1:4">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -6489,11 +6561,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="9" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:4">
@@ -6501,11 +6573,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="9" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:4">
@@ -6513,11 +6585,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="9" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" ht="13.5" spans="1:4">
@@ -6525,11 +6597,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="9" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="1:4">
@@ -6537,11 +6609,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" ht="13.5" spans="1:4">
@@ -6549,11 +6621,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" ht="13.5" spans="1:4">
@@ -6561,11 +6633,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" ht="13.5" spans="1:4">
@@ -6573,11 +6645,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" ht="13.5" spans="1:4">
@@ -6585,11 +6657,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="9" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" ht="13.5" spans="1:4">
@@ -6597,11 +6669,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="9" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" ht="13.5" spans="1:4">
@@ -6609,11 +6681,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="9" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" ht="13.5" spans="1:4">
@@ -6621,11 +6693,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:4">
@@ -6633,11 +6705,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="9" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" ht="13.5" spans="1:4">
@@ -6645,11 +6717,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" ht="13.5" spans="1:4">
@@ -6657,11 +6729,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="17" ht="13.5" spans="1:4">
@@ -6669,11 +6741,11 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="9" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="18" ht="13.5" spans="1:4">
@@ -6681,11 +6753,11 @@
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" ht="13.5" spans="1:4">
@@ -6693,11 +6765,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" ht="13.5" spans="1:4">
@@ -6705,11 +6777,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" ht="13.5" spans="1:4">
@@ -6717,11 +6789,11 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="9" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" ht="13.5" spans="1:4">
@@ -6729,11 +6801,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="9" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" ht="13.5" spans="1:4">
@@ -6741,11 +6813,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="9" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -6759,55 +6831,65 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultColWidth="8.8952380952381" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="68.552380952381" style="1" customWidth="1"/>
+    <col min="1" max="1" width="106" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="2" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
